--- a/AAII_Financials/Yearly/HMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HMC_YR_FIN.xlsx
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>137081300</v>
+      </c>
+      <c r="E8" s="3">
         <v>144835100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>135062000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>127188900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>119840400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>119083500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>138761400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>143386100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>144636700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>94354600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>107318500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>113688700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>114555800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>89790500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71850800</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>114116500</v>
+      </c>
+      <c r="E9" s="3">
         <v>113689600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>105891800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>102126900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>95261000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>94392300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>110143500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>113025500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>112994500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>73235800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>83293100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>88121600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>87849500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66767500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>53513500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>22964700</v>
+      </c>
+      <c r="E10" s="3">
         <v>31145500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29170200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25062000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24579400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24691300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28618000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30360600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31642200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21118800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24025300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25567100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26706300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23023000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18337300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>9689300</v>
+      </c>
+      <c r="E12" s="3">
         <v>7342200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6106400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6626700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6481300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6680800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7473100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7281900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7079300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4660200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4825300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5170600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5481100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5092900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4699200</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,14 +998,17 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>42</v>
+      <c r="D14" s="3">
+        <v>303900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>42</v>
@@ -1006,15 +1025,15 @@
       <c r="I14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" s="3">
         <v>614500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>506000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1030,39 +1049,42 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>3053100</v>
+        <v>8596000</v>
       </c>
       <c r="E15" s="3">
-        <v>3219100</v>
+        <v>8908700</v>
       </c>
       <c r="F15" s="3">
+        <v>5251800</v>
+      </c>
+      <c r="G15" s="3">
         <v>5428500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5032100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5644200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6504300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5898400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6714300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>139383200</v>
+      </c>
+      <c r="E17" s="3">
         <v>136731600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>125925300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>121315500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>112665800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>113114100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>132872700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>136216500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>136282200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>88688200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>103618600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>107968400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>107009200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>84838200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>69759200</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-2301900</v>
+      </c>
+      <c r="E18" s="3">
         <v>8103500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9136700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5873400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7174500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5969400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5888700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7169600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8354600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5666400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3699800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5720200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7546600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4952300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2091500</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>631700</v>
+      </c>
+      <c r="E20" s="3">
         <v>314600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-909300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-418900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1526900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2211100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1174400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1917900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2339500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1204700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1104100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1312200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1125200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-397800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>329200</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>10842000</v>
+        <v>5662400</v>
       </c>
       <c r="E21" s="3">
-        <v>13265100</v>
+        <v>16697600</v>
       </c>
       <c r="F21" s="3">
+        <v>15297900</v>
+      </c>
+      <c r="G21" s="3">
         <v>11720700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13733500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13824600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13567400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14985900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17408400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11436300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9613900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12428100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14082600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9933700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7442300</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>525500</v>
+      </c>
+      <c r="E22" s="3">
         <v>366700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>394200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>271700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>138900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>125500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>229400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>119300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>122100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>84100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>133400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>155200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>117300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>110500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>93800</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-2536400</v>
+      </c>
+      <c r="E23" s="3">
         <v>8799000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10858400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6616600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8812900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8264600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7341100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8838300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10498300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6787100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4670600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6877200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8554600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4444000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2326900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-316200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2768700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3039900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1220600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2548600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1976600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2602100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2735200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-128700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2208000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1683800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2091000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2454800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1626900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1227000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-2220200</v>
+      </c>
+      <c r="E26" s="3">
         <v>6030400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7818500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5396000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6264300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6288000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4739100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6103100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10627000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4579100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2986700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4786200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6099700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2817100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1099900</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-2666200</v>
+      </c>
+      <c r="E27" s="3">
         <v>5581600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7319900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4900300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5822600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5944200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4235500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5507800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9974500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4155700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2532300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4345500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6935700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3337400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1911800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-631700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-314600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>909300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>418900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1526900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2211100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1174400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1917900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2339500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1204700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1104100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1312200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1125200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>397800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-329200</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-2666200</v>
+      </c>
+      <c r="E33" s="3">
         <v>5581600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7319900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4900300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5822600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5944200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4235500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5507800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9974500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4155700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2532300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4345500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6935700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3337400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1911800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-2666200</v>
+      </c>
+      <c r="E35" s="3">
         <v>5581600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7319900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4900300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5822600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5944200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4235500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5507800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9974500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4155700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2532300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4345500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6935700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3337400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1911800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>31865800</v>
+      </c>
+      <c r="E41" s="3">
         <v>30242800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32756400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28608300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30262800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>24937100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24835500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22508100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21246500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14194300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12917300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12553900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10933200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10963700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22547800</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1867700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1392200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1517900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1985100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1793100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2670100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1766300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1473500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2007200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1007100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>757300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>790800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>934500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3803700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3377000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>7990200</v>
+      </c>
+      <c r="E43" s="3">
         <v>7752000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8198700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7975900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7384800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7249700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5891200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7158600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7537000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17813600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20232600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24904500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>48501300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20443300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>34241300</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>15918800</v>
+      </c>
+      <c r="E44" s="3">
         <v>16498300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16151300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16302700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15799100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13974800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14503200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14319900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14344500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9194200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9652700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12780600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>16569000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11048200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18726900</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>5358800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3761300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2953700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2892400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3617800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3469300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3399300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3232900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2740000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1974600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2316100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2676400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4111800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2127700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6789700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>82228600</v>
+      </c>
+      <c r="E46" s="3">
         <v>78049500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>78493700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>72053400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>72808500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>68527700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67852000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66305300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>65206800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44183800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>45876000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>53706100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>50830300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>48386600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42841300</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>14714200</v>
+      </c>
+      <c r="E47" s="3">
         <v>14130900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14380400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13322500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14716300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13739100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10196800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10199300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10508700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27179000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29475400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38813300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>74633600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29517500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50608400</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>20102400</v>
+      </c>
+      <c r="E48" s="3">
         <v>21435500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21383800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23832200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25358700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27319500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28361000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26909500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28835100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>49236000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50109900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>55657200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>94385600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38565800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>65025200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1866100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1902400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1788400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1523600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1283500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7403000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1238300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1196100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1346400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5245000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6063300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6478800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6135200</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3413000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3817000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3319400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3417900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3497000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3099200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1948800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1467800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1591500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1933900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2460700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2517000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11252000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7475600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8759700</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>210743600</v>
+      </c>
+      <c r="E54" s="3">
         <v>205517700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>196847400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>185581300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>197417100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>198202800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>190158800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>184271500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>182186900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>127778000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>133985000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>157172000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>147004000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>123945000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>106560000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11204700</v>
+      </c>
+      <c r="E57" s="3">
         <v>11108600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10643200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10729600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10180300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9837900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8907500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10692900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11530800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6829700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7067800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8526500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18367000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8981000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17518500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>31966900</v>
+      </c>
+      <c r="E58" s="3">
         <v>30516700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27665900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25279400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>26267900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27727900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>30705200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>28777000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>27587000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18783900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20503700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24170300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>48046400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>19846600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>33922500</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14737500</v>
+      </c>
+      <c r="E59" s="3">
         <v>11038100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12500300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10875500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9904600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10358300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10018000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10208100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10026600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10976800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12635600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12521200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11605700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8341400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13281100</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>64177100</v>
+      </c>
+      <c r="E60" s="3">
         <v>57531000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55029500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50040800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>49445800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>51677300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53810200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53976400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52955100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36590400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40207100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>45218000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>43526500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>37169000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32361000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54865700</v>
+      </c>
+      <c r="E61" s="3">
         <v>48110000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>41726600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34758900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>43081000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>44952800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>41781600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37944600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37114600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27109600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27464200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>33491100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30205100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24641600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20204400</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6798800</v>
+      </c>
+      <c r="E62" s="3">
         <v>6628800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4544300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3921600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4101400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4437500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4133000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3389800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3377800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13058500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14630400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15487800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27511500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14817500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>26149500</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>134343000</v>
+      </c>
+      <c r="E66" s="3">
         <v>121190600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>110861000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>99055000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>108706000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>113456600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>113152600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>106969900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>104656700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78607500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>84288800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>96535800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>88970200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>78100000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>66854200</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58966600</v>
+      </c>
+      <c r="E72" s="3">
         <v>74272700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>70372600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>75075800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>78554100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>80482300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>75676500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>71957700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>71666400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45244900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45528200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51892900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>112779000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>54987500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>104637000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74321600</v>
+      </c>
+      <c r="E76" s="3">
         <v>82315100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>83944300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>84133900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>86242900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>82119200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74462000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74611700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74700200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49170300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>49696500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>60636600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58033500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45845400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>39705700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-2666200</v>
+      </c>
+      <c r="E81" s="3">
         <v>5581600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7319900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4900300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5822600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5944200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4235500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5507800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9974500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4155700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2532300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4345500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6935700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3337400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1911800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3551400</v>
+        <v>9067400</v>
       </c>
       <c r="E83" s="3">
-        <v>3728500</v>
+        <v>9406900</v>
       </c>
       <c r="F83" s="3">
+        <v>5251800</v>
+      </c>
+      <c r="G83" s="3">
         <v>5428500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5032100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5644200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6504300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5898400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6714300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4545000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4856200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5333200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5387300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5367400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5016000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7139800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1951000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4940500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16015600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13831600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9696100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9102200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7002900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9299700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5965400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10223800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8704000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4113800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7278800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6884300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3849300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3411100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2305200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3573600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2208100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2879000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3440400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3797200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3912800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3330400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4668500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5529200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24001700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12907800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9772100</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5359400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6290300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5733800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5100700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3096800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7205100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5757200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5212100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5791800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4385200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6431800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7169400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8436600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9724100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6084500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1788600</v>
+      </c>
+      <c r="E96" s="3">
         <v>2322600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1599100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1605900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1551500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1311900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1828900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1753200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1640400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1093300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1165700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1352900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1304200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1179600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-977600</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-232200</v>
+      </c>
+      <c r="E100" s="3">
         <v>1873000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6073500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11045800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5070400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2567700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-812400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>206900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1641500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>778000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>106500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3256000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1086900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-616800</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2160300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-376900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2333100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1094400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1886300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>851300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-876300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>146900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-449200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-991500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>731400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>361200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>985900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-471400</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3708600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2843200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7613300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>963500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7550700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>774600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1656400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2144500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1417200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2349000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2372600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-705600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-372600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-288500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
